--- a/table.xlsx
+++ b/table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\游戏数据\遐蝶周边\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABBB5D1-B5BE-4663-822B-DC902FACAE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC994791-5526-47D3-9490-8E00A6074D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="381">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1390,6 +1390,25 @@
   </si>
   <si>
     <t>26041509.webp</t>
+  </si>
+  <si>
+    <t>与你同行的回忆系列纸雕灯</t>
+  </si>
+  <si>
+    <t>密度板 铜版纸 电子元件 亚克力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纸雕工艺、无极调光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约255×158×60mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26052101.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1715,7 +1734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
@@ -4356,6 +4375,32 @@
         <v>375</v>
       </c>
     </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>20260521</v>
+      </c>
+      <c r="C103" t="s">
+        <v>376</v>
+      </c>
+      <c r="D103">
+        <v>129</v>
+      </c>
+      <c r="E103" t="s">
+        <v>377</v>
+      </c>
+      <c r="F103" t="s">
+        <v>378</v>
+      </c>
+      <c r="G103" t="s">
+        <v>379</v>
+      </c>
+      <c r="H103" t="s">
+        <v>380</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table.xlsx
+++ b/table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\游戏数据\遐蝶周边\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC994791-5526-47D3-9490-8E00A6074D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354E63BB-5BAF-4EC7-9CA4-163DF4F78659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="386">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1408,6 +1408,24 @@
   </si>
   <si>
     <t>26052101.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如我所书系列彩胶礼盒</t>
+  </si>
+  <si>
+    <t>26053101.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄金裔小卡-遐蝶款A</t>
+  </si>
+  <si>
+    <t>约62×100mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26053102.webp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1734,14 +1752,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.75" customWidth="1"/>
     <col min="4" max="4" width="5.1640625" customWidth="1"/>
-    <col min="5" max="5" width="53.75" customWidth="1"/>
+    <col min="5" max="5" width="53.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="44" customWidth="1"/>
     <col min="7" max="7" width="68.1640625" customWidth="1"/>
     <col min="8" max="8" width="18.25" bestFit="1" customWidth="1"/>
@@ -4401,6 +4419,46 @@
         <v>380</v>
       </c>
     </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>20260531</v>
+      </c>
+      <c r="C104" t="s">
+        <v>381</v>
+      </c>
+      <c r="D104">
+        <v>309</v>
+      </c>
+      <c r="H104" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>20260531</v>
+      </c>
+      <c r="C105" t="s">
+        <v>383</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+      <c r="E105" t="s">
+        <v>9</v>
+      </c>
+      <c r="G105" t="s">
+        <v>384</v>
+      </c>
+      <c r="H105" t="s">
+        <v>385</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table.xlsx
+++ b/table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\游戏数据\遐蝶周边\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354E63BB-5BAF-4EC7-9CA4-163DF4F78659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD1205F-6DD8-4ECD-AAEE-BCC4EB6A27FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$127</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="460">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1427,6 +1427,251 @@
   <si>
     <t>26053102.webp</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列外套</t>
+  </si>
+  <si>
+    <t>尼龙面料</t>
+  </si>
+  <si>
+    <t>0.3格子 消光塔丝隆</t>
+  </si>
+  <si>
+    <t>索罗娜平纹布</t>
+  </si>
+  <si>
+    <t>30D弹力面料</t>
+  </si>
+  <si>
+    <t>网眼布</t>
+  </si>
+  <si>
+    <t>全棉汗布</t>
+  </si>
+  <si>
+    <t>针织面料</t>
+  </si>
+  <si>
+    <t>消光破卡面料</t>
+  </si>
+  <si>
+    <t>涤锦梭织面料</t>
+  </si>
+  <si>
+    <t>合成革+织物</t>
+  </si>
+  <si>
+    <t>聚氨酯合成革(PU)、尼龙</t>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列宽松T恤A-浅灰色拼接T恤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列宽松T恤B-速干凉感拼接T恤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列宽松T恤C-深灰色连肩T恤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3格子 消光塔丝隆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列假两件T恤</t>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列短袖衬衫</t>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列短裤</t>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列花苞裙</t>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列运动鞋</t>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列双肩包</t>
+  </si>
+  <si>
+    <t>遐蝶主题印象系列挎包</t>
+  </si>
+  <si>
+    <t>约520x330x230mm 容量约20L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约340x170x120mm(不含手提) 手提高度约340mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26061501.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26061502.webp</t>
+  </si>
+  <si>
+    <t>26061503.webp</t>
+  </si>
+  <si>
+    <t>26061504.webp</t>
+  </si>
+  <si>
+    <t>26061505.webp</t>
+  </si>
+  <si>
+    <t>26061506.webp</t>
+  </si>
+  <si>
+    <t>26061507.webp</t>
+  </si>
+  <si>
+    <t>26061508.webp</t>
+  </si>
+  <si>
+    <t>26061509.webp</t>
+  </si>
+  <si>
+    <t>26061510.webp</t>
+  </si>
+  <si>
+    <t>26061511.webp</t>
+  </si>
+  <si>
+    <t>与你同行的回忆系列短袖T恤</t>
+  </si>
+  <si>
+    <t>索罗娜汗布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26061512.webp</t>
+  </si>
+  <si>
+    <t>列车环游记系列马口铁徽章</t>
+  </si>
+  <si>
+    <t>拉丝银葱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拉丝银葱垫纸+烫光柱镭射金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列车环游记系列亚克力立牌</t>
+  </si>
+  <si>
+    <t>局部烫印</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约173×100mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列车环游记系列亚克力挂件</t>
+  </si>
+  <si>
+    <t>镭射覆膜+烫印</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约67×85mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列车环游记系列镭射票</t>
+  </si>
+  <si>
+    <t>约210×78mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逆向UV+荧光UV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗷呜嗷呜系列坐姿毛绒玩偶</t>
+  </si>
+  <si>
+    <t>26061513.webp</t>
+  </si>
+  <si>
+    <t>26061514.webp</t>
+  </si>
+  <si>
+    <t>26061515.webp</t>
+  </si>
+  <si>
+    <t>26061516.webp</t>
+  </si>
+  <si>
+    <t>26061517.webp</t>
+  </si>
+  <si>
+    <t>100%聚酯纤维/铁线（尾巴有铁线）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>刺绣，移印，丝印</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高约18cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>列车环游记系列Q版马口铁徽章</t>
+  </si>
+  <si>
+    <t>列车环游记系列Q版亚克力立牌</t>
+  </si>
+  <si>
+    <t>整版印刷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约131.5×94.6mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26061518.webp</t>
+  </si>
+  <si>
+    <t>26061519.webp</t>
+  </si>
+  <si>
+    <t>列车环游记系列Q版收藏卡</t>
+  </si>
+  <si>
+    <t>局部逆向UV</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银河潮流指南系列马口铁徽章-遐蝶</t>
+  </si>
+  <si>
+    <t>银河潮流指南系列亚克力合影棒-遐蝶</t>
+  </si>
+  <si>
+    <t>棒身约1.2×10cm 合影页面约10.5×8.5cm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26061520.webp</t>
+  </si>
+  <si>
+    <t>26061521.webp</t>
+  </si>
+  <si>
+    <t>26061522.webp</t>
   </si>
 </sst>
 </file>
@@ -1752,7 +1997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
@@ -4459,6 +4704,518 @@
         <v>385</v>
       </c>
     </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>20260615</v>
+      </c>
+      <c r="C106" t="s">
+        <v>386</v>
+      </c>
+      <c r="D106">
+        <v>449</v>
+      </c>
+      <c r="E106" t="s">
+        <v>387</v>
+      </c>
+      <c r="F106" t="s">
+        <v>401</v>
+      </c>
+      <c r="H106" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>20260615</v>
+      </c>
+      <c r="C107" t="s">
+        <v>398</v>
+      </c>
+      <c r="D107">
+        <v>149</v>
+      </c>
+      <c r="E107" t="s">
+        <v>389</v>
+      </c>
+      <c r="H107" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>20260615</v>
+      </c>
+      <c r="C108" t="s">
+        <v>399</v>
+      </c>
+      <c r="D108">
+        <v>199</v>
+      </c>
+      <c r="E108" t="s">
+        <v>390</v>
+      </c>
+      <c r="F108" t="s">
+        <v>391</v>
+      </c>
+      <c r="H108" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>20260615</v>
+      </c>
+      <c r="C109" t="s">
+        <v>400</v>
+      </c>
+      <c r="D109">
+        <v>149</v>
+      </c>
+      <c r="E109" t="s">
+        <v>392</v>
+      </c>
+      <c r="H109" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>20260615</v>
+      </c>
+      <c r="C110" t="s">
+        <v>402</v>
+      </c>
+      <c r="D110">
+        <v>149</v>
+      </c>
+      <c r="E110" t="s">
+        <v>393</v>
+      </c>
+      <c r="H110" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>20260615</v>
+      </c>
+      <c r="C111" t="s">
+        <v>403</v>
+      </c>
+      <c r="D111">
+        <v>269</v>
+      </c>
+      <c r="E111" t="s">
+        <v>394</v>
+      </c>
+      <c r="H111" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>20260615</v>
+      </c>
+      <c r="C112" t="s">
+        <v>404</v>
+      </c>
+      <c r="D112">
+        <v>249</v>
+      </c>
+      <c r="E112" t="s">
+        <v>388</v>
+      </c>
+      <c r="F112" t="s">
+        <v>387</v>
+      </c>
+      <c r="H112" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>20260615</v>
+      </c>
+      <c r="C113" t="s">
+        <v>405</v>
+      </c>
+      <c r="D113">
+        <v>249</v>
+      </c>
+      <c r="E113" t="s">
+        <v>395</v>
+      </c>
+      <c r="H113" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>20260615</v>
+      </c>
+      <c r="C114" t="s">
+        <v>406</v>
+      </c>
+      <c r="D114">
+        <v>399</v>
+      </c>
+      <c r="E114" t="s">
+        <v>396</v>
+      </c>
+      <c r="H114" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>20260615</v>
+      </c>
+      <c r="C115" t="s">
+        <v>407</v>
+      </c>
+      <c r="D115">
+        <v>349</v>
+      </c>
+      <c r="E115" t="s">
+        <v>387</v>
+      </c>
+      <c r="G115" t="s">
+        <v>409</v>
+      </c>
+      <c r="H115" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>20260615</v>
+      </c>
+      <c r="C116" t="s">
+        <v>408</v>
+      </c>
+      <c r="D116">
+        <v>329</v>
+      </c>
+      <c r="E116" t="s">
+        <v>397</v>
+      </c>
+      <c r="G116" t="s">
+        <v>410</v>
+      </c>
+      <c r="H116" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>20260615</v>
+      </c>
+      <c r="C117" t="s">
+        <v>422</v>
+      </c>
+      <c r="D117">
+        <v>129</v>
+      </c>
+      <c r="E117" t="s">
+        <v>423</v>
+      </c>
+      <c r="H117" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>20260615</v>
+      </c>
+      <c r="C118" t="s">
+        <v>425</v>
+      </c>
+      <c r="D118">
+        <v>15</v>
+      </c>
+      <c r="E118" t="s">
+        <v>6</v>
+      </c>
+      <c r="F118" t="s">
+        <v>427</v>
+      </c>
+      <c r="G118" t="s">
+        <v>8</v>
+      </c>
+      <c r="H118" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>20260615</v>
+      </c>
+      <c r="C119" t="s">
+        <v>428</v>
+      </c>
+      <c r="D119">
+        <v>48</v>
+      </c>
+      <c r="E119" t="s">
+        <v>51</v>
+      </c>
+      <c r="F119" t="s">
+        <v>429</v>
+      </c>
+      <c r="G119" t="s">
+        <v>430</v>
+      </c>
+      <c r="H119" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>20260615</v>
+      </c>
+      <c r="C120" t="s">
+        <v>431</v>
+      </c>
+      <c r="D120">
+        <v>32</v>
+      </c>
+      <c r="E120" t="s">
+        <v>51</v>
+      </c>
+      <c r="F120" t="s">
+        <v>432</v>
+      </c>
+      <c r="G120" t="s">
+        <v>433</v>
+      </c>
+      <c r="H120" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>20260615</v>
+      </c>
+      <c r="C121" t="s">
+        <v>434</v>
+      </c>
+      <c r="D121">
+        <v>15</v>
+      </c>
+      <c r="E121" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" t="s">
+        <v>436</v>
+      </c>
+      <c r="G121" t="s">
+        <v>435</v>
+      </c>
+      <c r="H121" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>20260615</v>
+      </c>
+      <c r="C122" t="s">
+        <v>437</v>
+      </c>
+      <c r="D122">
+        <v>129</v>
+      </c>
+      <c r="E122" t="s">
+        <v>443</v>
+      </c>
+      <c r="F122" t="s">
+        <v>444</v>
+      </c>
+      <c r="G122" t="s">
+        <v>445</v>
+      </c>
+      <c r="H122" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>20260615</v>
+      </c>
+      <c r="C123" t="s">
+        <v>446</v>
+      </c>
+      <c r="D123">
+        <v>15</v>
+      </c>
+      <c r="E123" t="s">
+        <v>6</v>
+      </c>
+      <c r="F123" t="s">
+        <v>311</v>
+      </c>
+      <c r="G123" t="s">
+        <v>170</v>
+      </c>
+      <c r="H123" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>20260615</v>
+      </c>
+      <c r="C124" t="s">
+        <v>447</v>
+      </c>
+      <c r="D124">
+        <v>35</v>
+      </c>
+      <c r="E124" t="s">
+        <v>51</v>
+      </c>
+      <c r="F124" t="s">
+        <v>448</v>
+      </c>
+      <c r="G124" t="s">
+        <v>449</v>
+      </c>
+      <c r="H124" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>20260615</v>
+      </c>
+      <c r="C125" t="s">
+        <v>452</v>
+      </c>
+      <c r="D125">
+        <v>15</v>
+      </c>
+      <c r="E125" t="s">
+        <v>9</v>
+      </c>
+      <c r="F125" t="s">
+        <v>453</v>
+      </c>
+      <c r="G125" t="s">
+        <v>27</v>
+      </c>
+      <c r="H125" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>20260615</v>
+      </c>
+      <c r="C126" t="s">
+        <v>454</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126" t="s">
+        <v>6</v>
+      </c>
+      <c r="F126" t="s">
+        <v>426</v>
+      </c>
+      <c r="G126" t="s">
+        <v>207</v>
+      </c>
+      <c r="H126" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>20260615</v>
+      </c>
+      <c r="C127" t="s">
+        <v>455</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127" t="s">
+        <v>51</v>
+      </c>
+      <c r="G127" t="s">
+        <v>456</v>
+      </c>
+      <c r="H127" t="s">
+        <v>459</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table.xlsx
+++ b/table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\游戏数据\遐蝶周边\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD1205F-6DD8-4ECD-AAEE-BCC4EB6A27FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBFB38A-64B4-498D-90FA-7E035A3E6B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/table.xlsx
+++ b/table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\游戏数据\遐蝶周边\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFBFB38A-64B4-498D-90FA-7E035A3E6B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D83B3F-9586-456B-A853-34BC55CC6918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$128</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="463">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1672,6 +1672,17 @@
   </si>
   <si>
     <t>26061522.webp</t>
+  </si>
+  <si>
+    <t>与你同行的回忆系列明信片套组</t>
+  </si>
+  <si>
+    <t>约102×165mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26031104.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1997,7 +2008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.83203125" bestFit="1" customWidth="1"/>
@@ -4412,25 +4423,25 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>20260415</v>
+        <v>20260311</v>
       </c>
       <c r="C94" t="s">
-        <v>340</v>
+        <v>460</v>
       </c>
       <c r="D94">
-        <v>349</v>
+        <v>80</v>
       </c>
       <c r="E94" t="s">
-        <v>60</v>
+        <v>337</v>
       </c>
       <c r="F94" t="s">
-        <v>61</v>
+        <v>338</v>
       </c>
       <c r="G94" t="s">
-        <v>341</v>
+        <v>461</v>
       </c>
       <c r="H94" t="s">
-        <v>342</v>
+        <v>462</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
@@ -4441,19 +4452,22 @@
         <v>20260415</v>
       </c>
       <c r="C95" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D95">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="E95" t="s">
-        <v>345</v>
+        <v>60</v>
+      </c>
+      <c r="F95" t="s">
+        <v>61</v>
       </c>
       <c r="G95" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="H95" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
@@ -4464,22 +4478,19 @@
         <v>20260415</v>
       </c>
       <c r="C96" t="s">
-        <v>372</v>
+        <v>344</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="E96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G96" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H96" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
@@ -4490,22 +4501,22 @@
         <v>20260415</v>
       </c>
       <c r="C97" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="D97">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
       <c r="G97" t="s">
-        <v>207</v>
+        <v>348</v>
       </c>
       <c r="H97" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
@@ -4516,22 +4527,22 @@
         <v>20260415</v>
       </c>
       <c r="C98" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D98">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="E98" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="F98" t="s">
-        <v>31</v>
+        <v>311</v>
       </c>
       <c r="G98" t="s">
-        <v>356</v>
+        <v>207</v>
       </c>
       <c r="H98" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
@@ -4542,22 +4553,22 @@
         <v>20260415</v>
       </c>
       <c r="C99" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D99">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="E99" t="s">
         <v>51</v>
       </c>
       <c r="F99" t="s">
-        <v>358</v>
+        <v>31</v>
       </c>
       <c r="G99" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="H99" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
@@ -4568,22 +4579,22 @@
         <v>20260415</v>
       </c>
       <c r="C100" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="D100">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E100" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F100" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="G100" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="H100" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
@@ -4594,22 +4605,22 @@
         <v>20260415</v>
       </c>
       <c r="C101" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D101">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
-        <v>369</v>
+        <v>9</v>
       </c>
       <c r="F101" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="G101" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H101" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
@@ -4620,22 +4631,22 @@
         <v>20260415</v>
       </c>
       <c r="C102" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E102" t="s">
-        <v>6</v>
+        <v>369</v>
       </c>
       <c r="F102" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="G102" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="H102" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
@@ -4643,25 +4654,25 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>20260521</v>
+        <v>20260415</v>
       </c>
       <c r="C103" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D103">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="E103" t="s">
-        <v>377</v>
+        <v>6</v>
       </c>
       <c r="F103" t="s">
-        <v>378</v>
+        <v>311</v>
       </c>
       <c r="G103" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="H103" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
@@ -4669,16 +4680,25 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>20260531</v>
+        <v>20260521</v>
       </c>
       <c r="C104" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D104">
-        <v>309</v>
+        <v>129</v>
+      </c>
+      <c r="E104" t="s">
+        <v>377</v>
+      </c>
+      <c r="F104" t="s">
+        <v>378</v>
+      </c>
+      <c r="G104" t="s">
+        <v>379</v>
       </c>
       <c r="H104" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
@@ -4689,19 +4709,13 @@
         <v>20260531</v>
       </c>
       <c r="C105" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D105">
-        <v>0</v>
-      </c>
-      <c r="E105" t="s">
-        <v>9</v>
-      </c>
-      <c r="G105" t="s">
-        <v>384</v>
+        <v>309</v>
       </c>
       <c r="H105" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
@@ -4709,22 +4723,22 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>20260615</v>
+        <v>20260531</v>
       </c>
       <c r="C106" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D106">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="E106" t="s">
-        <v>387</v>
-      </c>
-      <c r="F106" t="s">
-        <v>401</v>
+        <v>9</v>
+      </c>
+      <c r="G106" t="s">
+        <v>384</v>
       </c>
       <c r="H106" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
@@ -4735,16 +4749,19 @@
         <v>20260615</v>
       </c>
       <c r="C107" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="D107">
-        <v>149</v>
+        <v>449</v>
       </c>
       <c r="E107" t="s">
-        <v>389</v>
+        <v>387</v>
+      </c>
+      <c r="F107" t="s">
+        <v>401</v>
       </c>
       <c r="H107" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
@@ -4755,19 +4772,16 @@
         <v>20260615</v>
       </c>
       <c r="C108" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D108">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="E108" t="s">
-        <v>390</v>
-      </c>
-      <c r="F108" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H108" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
@@ -4778,16 +4792,19 @@
         <v>20260615</v>
       </c>
       <c r="C109" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D109">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="E109" t="s">
-        <v>392</v>
+        <v>390</v>
+      </c>
+      <c r="F109" t="s">
+        <v>391</v>
       </c>
       <c r="H109" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
@@ -4798,16 +4815,16 @@
         <v>20260615</v>
       </c>
       <c r="C110" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D110">
         <v>149</v>
       </c>
       <c r="E110" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H110" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
@@ -4818,16 +4835,16 @@
         <v>20260615</v>
       </c>
       <c r="C111" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D111">
-        <v>269</v>
+        <v>149</v>
       </c>
       <c r="E111" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H111" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
@@ -4838,19 +4855,16 @@
         <v>20260615</v>
       </c>
       <c r="C112" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D112">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="E112" t="s">
-        <v>388</v>
-      </c>
-      <c r="F112" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="H112" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
@@ -4861,16 +4875,19 @@
         <v>20260615</v>
       </c>
       <c r="C113" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D113">
         <v>249</v>
       </c>
       <c r="E113" t="s">
-        <v>395</v>
+        <v>388</v>
+      </c>
+      <c r="F113" t="s">
+        <v>387</v>
       </c>
       <c r="H113" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
@@ -4881,16 +4898,16 @@
         <v>20260615</v>
       </c>
       <c r="C114" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D114">
-        <v>399</v>
+        <v>249</v>
       </c>
       <c r="E114" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H114" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
@@ -4901,19 +4918,16 @@
         <v>20260615</v>
       </c>
       <c r="C115" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D115">
-        <v>349</v>
+        <v>399</v>
       </c>
       <c r="E115" t="s">
-        <v>387</v>
-      </c>
-      <c r="G115" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="H115" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
@@ -4924,19 +4938,19 @@
         <v>20260615</v>
       </c>
       <c r="C116" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D116">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="E116" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="G116" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H116" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
@@ -4947,16 +4961,19 @@
         <v>20260615</v>
       </c>
       <c r="C117" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="D117">
-        <v>129</v>
+        <v>329</v>
       </c>
       <c r="E117" t="s">
-        <v>423</v>
+        <v>397</v>
+      </c>
+      <c r="G117" t="s">
+        <v>410</v>
       </c>
       <c r="H117" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
@@ -4967,22 +4984,16 @@
         <v>20260615</v>
       </c>
       <c r="C118" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D118">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="E118" t="s">
-        <v>6</v>
-      </c>
-      <c r="F118" t="s">
-        <v>427</v>
-      </c>
-      <c r="G118" t="s">
-        <v>8</v>
+        <v>423</v>
       </c>
       <c r="H118" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
@@ -4993,22 +5004,22 @@
         <v>20260615</v>
       </c>
       <c r="C119" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D119">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="E119" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="F119" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G119" t="s">
-        <v>430</v>
+        <v>8</v>
       </c>
       <c r="H119" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
@@ -5019,22 +5030,22 @@
         <v>20260615</v>
       </c>
       <c r="C120" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D120">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E120" t="s">
         <v>51</v>
       </c>
       <c r="F120" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="G120" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H120" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
@@ -5045,22 +5056,22 @@
         <v>20260615</v>
       </c>
       <c r="C121" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D121">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E121" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F121" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="G121" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H121" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
@@ -5071,22 +5082,22 @@
         <v>20260615</v>
       </c>
       <c r="C122" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D122">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="E122" t="s">
-        <v>443</v>
+        <v>9</v>
       </c>
       <c r="F122" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="G122" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="H122" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
@@ -5097,22 +5108,22 @@
         <v>20260615</v>
       </c>
       <c r="C123" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="D123">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="E123" t="s">
-        <v>6</v>
+        <v>443</v>
       </c>
       <c r="F123" t="s">
-        <v>311</v>
+        <v>444</v>
       </c>
       <c r="G123" t="s">
-        <v>170</v>
+        <v>445</v>
       </c>
       <c r="H123" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
@@ -5123,22 +5134,22 @@
         <v>20260615</v>
       </c>
       <c r="C124" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D124">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E124" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="F124" t="s">
-        <v>448</v>
+        <v>311</v>
       </c>
       <c r="G124" t="s">
-        <v>449</v>
+        <v>170</v>
       </c>
       <c r="H124" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
@@ -5149,22 +5160,22 @@
         <v>20260615</v>
       </c>
       <c r="C125" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="D125">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E125" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="F125" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="G125" t="s">
-        <v>27</v>
+        <v>449</v>
       </c>
       <c r="H125" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
@@ -5175,22 +5186,22 @@
         <v>20260615</v>
       </c>
       <c r="C126" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E126" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F126" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="G126" t="s">
-        <v>207</v>
+        <v>27</v>
       </c>
       <c r="H126" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
@@ -5201,18 +5212,44 @@
         <v>20260615</v>
       </c>
       <c r="C127" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127" t="s">
+        <v>6</v>
+      </c>
+      <c r="F127" t="s">
+        <v>426</v>
+      </c>
+      <c r="G127" t="s">
+        <v>207</v>
+      </c>
+      <c r="H127" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>20260615</v>
+      </c>
+      <c r="C128" t="s">
+        <v>455</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128" t="s">
         <v>51</v>
       </c>
-      <c r="G127" t="s">
+      <c r="G128" t="s">
         <v>456</v>
       </c>
-      <c r="H127" t="s">
+      <c r="H128" t="s">
         <v>459</v>
       </c>
     </row>
